--- a/tests/e2e/fixtures/liste-blanche-test.xlsx
+++ b/tests/e2e/fixtures/liste-blanche-test.xlsx
@@ -23,7 +23,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Adresse Gmail</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
